--- a/_FACTORY/_LIGNES/_TEMPLATE/A3_TRAITEMENT/A3_THEME.xlsx
+++ b/_FACTORY/_LIGNES/_TEMPLATE/A3_TRAITEMENT/A3_THEME.xlsx
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Document de traçabilité des transformations BIB → BIPREGEN → ANGIPREGEN.</t>
+          <t>Document de traçabilité des décisions d'extraction BIB → A3.</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr"/>
@@ -1811,10 +1811,14 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>[non trouvé dans glossaire — vérifier source]</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
+          <t>Comportement obligatoire de signalement des opportunités de réduction de tokens avant chaque action ou tool call.</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>[RULE-TOKEN-MONITOR-001] CLAUDE SIGNALE CHAQUE OPPORTUNITÉ TOKEN — comportement obligatoire, tous contextes.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1844,26 +1848,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>MANQUANT</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>TOKEN_OPTIMIZATION_MONITORING — présent dans config step mais absent du glossaire</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>→ Ajouter dans glossaire_documentaire_factory.md</t>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Aucune alerte automatique — vérification manuelle recommandée à chaque étape</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-19</t>
+          <t>sync_glossaire.py — dernière exécution automatique — 2026-05-21</t>
         </is>
       </c>
     </row>
